--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.99841120959515</v>
+        <v>7.312241821559213</v>
       </c>
       <c r="D2" t="n">
-        <v>5.099019513592784</v>
+        <v>0.8285906709588275</v>
       </c>
       <c r="E2" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F2" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.04973585154604</v>
+        <v>4.233082075876232</v>
       </c>
       <c r="D3" t="n">
-        <v>25.43874375801205</v>
+        <v>4.133795860676958</v>
       </c>
       <c r="E3" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F3" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.42122762550053</v>
+        <v>3.805949489143837</v>
       </c>
       <c r="D4" t="n">
-        <v>21.55334734227764</v>
+        <v>3.502418943120117</v>
       </c>
       <c r="E4" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F4" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.4609186346275</v>
+        <v>6.574899278126969</v>
       </c>
       <c r="D5" t="n">
-        <v>23.04886114323222</v>
+        <v>3.745439935775236</v>
       </c>
       <c r="E5" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F5" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.66019815820585</v>
+        <v>4.169782200708451</v>
       </c>
       <c r="D6" t="n">
-        <v>25.26470723565424</v>
+        <v>4.105514925793814</v>
       </c>
       <c r="E6" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F6" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.28026374216603</v>
+        <v>5.570542858101979</v>
       </c>
       <c r="D7" t="n">
-        <v>32.50223508111709</v>
+        <v>5.281613200681527</v>
       </c>
       <c r="E7" t="n">
-        <v>8.099032533532677</v>
+        <v>1.31609278669906</v>
       </c>
       <c r="F7" t="n">
-        <v>8.362474525856845</v>
+        <v>1.358902110451737</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
